--- a/resultados/previsoes_uni_2020.xlsx
+++ b/resultados/previsoes_uni_2020.xlsx
@@ -468,7 +468,7 @@
         <v>12697109863.15224</v>
       </c>
       <c r="G2">
-        <v>12717020343.36886</v>
+        <v>12426645163.41712</v>
       </c>
       <c r="H2">
         <v>12717020343.36886</v>
@@ -503,7 +503,7 @@
         <v>11972999006.25738</v>
       </c>
       <c r="G3">
-        <v>11995061575.82377</v>
+        <v>11693115393.85064</v>
       </c>
       <c r="H3">
         <v>11995061575.82377</v>
@@ -538,7 +538,7 @@
         <v>12202926313.46094</v>
       </c>
       <c r="G4">
-        <v>12230332881.12255</v>
+        <v>11934849499.94579</v>
       </c>
       <c r="H4">
         <v>12230332881.12255</v>
@@ -573,7 +573,7 @@
         <v>12687261869.71071</v>
       </c>
       <c r="G5">
-        <v>12717484065.2532</v>
+        <v>12437716131.44168</v>
       </c>
       <c r="H5">
         <v>12717484065.2532</v>
@@ -608,7 +608,7 @@
         <v>12649579414.25809</v>
       </c>
       <c r="G6">
-        <v>12655480199.78232</v>
+        <v>12218944811.80981</v>
       </c>
       <c r="H6">
         <v>12655480199.78232</v>
@@ -643,7 +643,7 @@
         <v>12732735247.32689</v>
       </c>
       <c r="G7">
-        <v>12734885262.04663</v>
+        <v>12348913021.36448</v>
       </c>
       <c r="H7">
         <v>12734885262.04663</v>
@@ -678,7 +678,7 @@
         <v>12814682831.65024</v>
       </c>
       <c r="G8">
-        <v>12791098633.30106</v>
+        <v>12436005105.47107</v>
       </c>
       <c r="H8">
         <v>12791098633.30106</v>
@@ -713,7 +713,7 @@
         <v>12974595130.31832</v>
       </c>
       <c r="G9">
-        <v>12961420776.55541</v>
+        <v>12786883292.39492</v>
       </c>
       <c r="H9">
         <v>12961420776.55541</v>
@@ -748,7 +748,7 @@
         <v>13413161034.97825</v>
       </c>
       <c r="G10">
-        <v>13376077519.4111</v>
+        <v>13081833940.72378</v>
       </c>
       <c r="H10">
         <v>13376077519.4111</v>
@@ -783,7 +783,7 @@
         <v>13676061213.35249</v>
       </c>
       <c r="G11">
-        <v>13640010111.61886</v>
+        <v>13350844172.41804</v>
       </c>
       <c r="H11">
         <v>13640010111.61886</v>
@@ -818,7 +818,7 @@
         <v>13599793091.09325</v>
       </c>
       <c r="G12">
-        <v>13572023042.75235</v>
+        <v>13450522363.59998</v>
       </c>
       <c r="H12">
         <v>13572023042.75235</v>
@@ -853,7 +853,7 @@
         <v>14552076274.80258</v>
       </c>
       <c r="G13">
-        <v>14510764825.42437</v>
+        <v>14206038500.59155</v>
       </c>
       <c r="H13">
         <v>14510764825.42437</v>
